--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718A2FD4-D5D3-462A-AE71-E89EF4342829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271C3803-9394-4383-A373-D08A01858D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31335" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -721,9 +721,6 @@
     <t>£34.57</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.onlineinsulation-sales.com', port=443): Max retries exceeded with url: /product/375mm-celotex-pl4025-pir-insulated-plasterboard-12m-x-24m/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.onlineinsulation-sales.com', port=443) at 0x182bdd20f50&gt;, 'Connection to www.onlineinsulation-sales.com timed out. (connect timeout=30)'))</t>
-  </si>
-  <si>
     <t>£55.73</t>
   </si>
   <si>
@@ -1208,6 +1205,9 @@
   </si>
   <si>
     <t>£26.25</t>
+  </si>
+  <si>
+    <t>£38.89</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1646,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -1735,7 +1735,7 @@
         <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R3" t="s">
         <v>40</v>
@@ -1758,7 +1758,7 @@
         <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -1791,7 +1791,7 @@
         <v>52</v>
       </c>
       <c r="Q4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R4" t="s">
         <v>53</v>
@@ -1814,7 +1814,7 @@
         <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G5" t="s">
         <v>57</v>
@@ -1847,7 +1847,7 @@
         <v>56</v>
       </c>
       <c r="Q5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R5" t="s">
         <v>65</v>
@@ -1870,7 +1870,7 @@
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G6" t="s">
         <v>69</v>
@@ -1882,7 +1882,7 @@
         <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K6" t="s">
         <v>72</v>
@@ -1903,7 +1903,7 @@
         <v>76</v>
       </c>
       <c r="Q6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R6" t="s">
         <v>77</v>
@@ -1926,7 +1926,7 @@
         <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G7" t="s">
         <v>81</v>
@@ -1959,7 +1959,7 @@
         <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R7" t="s">
         <v>90</v>
@@ -1982,7 +1982,7 @@
         <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G8" t="s">
         <v>94</v>
@@ -1994,7 +1994,7 @@
         <v>96</v>
       </c>
       <c r="J8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K8" t="s">
         <v>97</v>
@@ -2015,7 +2015,7 @@
         <v>93</v>
       </c>
       <c r="Q8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="R8" t="s">
         <v>101</v>
@@ -2038,7 +2038,7 @@
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G9" t="s">
         <v>104</v>
@@ -2071,7 +2071,7 @@
         <v>94</v>
       </c>
       <c r="Q9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R9" t="s">
         <v>112</v>
@@ -2094,7 +2094,7 @@
         <v>115</v>
       </c>
       <c r="F10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G10" t="s">
         <v>116</v>
@@ -2127,7 +2127,7 @@
         <v>124</v>
       </c>
       <c r="Q10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R10" t="s">
         <v>125</v>
@@ -2150,7 +2150,7 @@
         <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G11" t="s">
         <v>129</v>
@@ -2162,7 +2162,7 @@
         <v>131</v>
       </c>
       <c r="J11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K11" t="s">
         <v>132</v>
@@ -2183,7 +2183,7 @@
         <v>136</v>
       </c>
       <c r="Q11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="R11" t="s">
         <v>137</v>
@@ -2206,7 +2206,7 @@
         <v>140</v>
       </c>
       <c r="F12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G12" t="s">
         <v>141</v>
@@ -2239,7 +2239,7 @@
         <v>149</v>
       </c>
       <c r="Q12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R12" t="s">
         <v>150</v>
@@ -2262,7 +2262,7 @@
         <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G13" t="s">
         <v>154</v>
@@ -2274,7 +2274,7 @@
         <v>155</v>
       </c>
       <c r="J13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K13" t="s">
         <v>156</v>
@@ -2295,7 +2295,7 @@
         <v>159</v>
       </c>
       <c r="Q13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="R13" t="s">
         <v>160</v>
@@ -2318,7 +2318,7 @@
         <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G14" t="s">
         <v>164</v>
@@ -2351,7 +2351,7 @@
         <v>171</v>
       </c>
       <c r="Q14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="R14" t="s">
         <v>172</v>
@@ -2374,7 +2374,7 @@
         <v>175</v>
       </c>
       <c r="F15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G15" t="s">
         <v>176</v>
@@ -2386,7 +2386,7 @@
         <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K15" t="s">
         <v>179</v>
@@ -2407,7 +2407,7 @@
         <v>175</v>
       </c>
       <c r="Q15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R15" t="s">
         <v>183</v>
@@ -2442,7 +2442,7 @@
         <v>189</v>
       </c>
       <c r="J16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K16" t="s">
         <v>190</v>
@@ -2463,7 +2463,7 @@
         <v>186</v>
       </c>
       <c r="Q16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R16" t="s">
         <v>21</v>
@@ -2519,7 +2519,7 @@
         <v>205</v>
       </c>
       <c r="Q17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R17" t="s">
         <v>206</v>
@@ -2542,7 +2542,7 @@
         <v>209</v>
       </c>
       <c r="F18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G18" t="s">
         <v>21</v>
@@ -2575,7 +2575,7 @@
         <v>209</v>
       </c>
       <c r="Q18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R18" t="s">
         <v>21</v>
@@ -2631,7 +2631,7 @@
         <v>227</v>
       </c>
       <c r="Q19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R19" t="s">
         <v>228</v>
@@ -2654,370 +2654,370 @@
         <v>231</v>
       </c>
       <c r="F20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G20" t="s">
         <v>232</v>
       </c>
       <c r="H20" t="s">
+        <v>395</v>
+      </c>
+      <c r="I20" t="s">
         <v>233</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
+        <v>361</v>
+      </c>
+      <c r="K20" t="s">
         <v>234</v>
-      </c>
-      <c r="J20" t="s">
-        <v>362</v>
-      </c>
-      <c r="K20" t="s">
-        <v>235</v>
       </c>
       <c r="L20" t="s">
         <v>22</v>
       </c>
       <c r="M20" t="s">
+        <v>235</v>
+      </c>
+      <c r="N20" t="s">
         <v>236</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>237</v>
-      </c>
-      <c r="O20" t="s">
-        <v>238</v>
       </c>
       <c r="P20" t="s">
         <v>231</v>
       </c>
       <c r="Q20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B21" t="s">
         <v>240</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F21" t="s">
+        <v>347</v>
+      </c>
+      <c r="G21" t="s">
         <v>242</v>
       </c>
-      <c r="D21" t="s">
-        <v>242</v>
-      </c>
-      <c r="E21" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" t="s">
-        <v>348</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>243</v>
-      </c>
-      <c r="H21" t="s">
-        <v>244</v>
       </c>
       <c r="I21" t="s">
         <v>189</v>
       </c>
       <c r="J21" t="s">
+        <v>244</v>
+      </c>
+      <c r="K21" t="s">
         <v>245</v>
-      </c>
-      <c r="K21" t="s">
-        <v>246</v>
       </c>
       <c r="L21" t="s">
         <v>22</v>
       </c>
       <c r="M21" t="s">
+        <v>246</v>
+      </c>
+      <c r="N21" t="s">
+        <v>236</v>
+      </c>
+      <c r="O21" t="s">
         <v>247</v>
       </c>
-      <c r="N21" t="s">
-        <v>237</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>382</v>
+      </c>
+      <c r="R21" t="s">
         <v>248</v>
-      </c>
-      <c r="P21" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>383</v>
-      </c>
-      <c r="R21" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" t="s">
         <v>250</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>251</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G22" t="s">
         <v>252</v>
       </c>
-      <c r="D22" t="s">
-        <v>252</v>
-      </c>
-      <c r="E22" t="s">
-        <v>252</v>
-      </c>
-      <c r="F22" t="s">
-        <v>349</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>253</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>254</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
+        <v>362</v>
+      </c>
+      <c r="K22" t="s">
         <v>255</v>
-      </c>
-      <c r="J22" t="s">
-        <v>363</v>
-      </c>
-      <c r="K22" t="s">
-        <v>256</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
       </c>
       <c r="M22" t="s">
+        <v>256</v>
+      </c>
+      <c r="N22" t="s">
+        <v>236</v>
+      </c>
+      <c r="O22" t="s">
         <v>257</v>
       </c>
-      <c r="N22" t="s">
-        <v>237</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>258</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
+        <v>383</v>
+      </c>
+      <c r="R22" t="s">
         <v>259</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>384</v>
-      </c>
-      <c r="R22" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" t="s">
         <v>261</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>262</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" t="s">
+        <v>349</v>
+      </c>
+      <c r="G23" t="s">
         <v>263</v>
       </c>
-      <c r="D23" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" t="s">
-        <v>350</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>264</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>265</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>266</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>267</v>
-      </c>
-      <c r="K23" t="s">
-        <v>268</v>
       </c>
       <c r="L23" t="s">
         <v>22</v>
       </c>
       <c r="M23" t="s">
+        <v>268</v>
+      </c>
+      <c r="N23" t="s">
+        <v>390</v>
+      </c>
+      <c r="O23" t="s">
         <v>269</v>
       </c>
-      <c r="N23" t="s">
-        <v>391</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>384</v>
+      </c>
+      <c r="R23" t="s">
         <v>270</v>
-      </c>
-      <c r="P23" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>385</v>
-      </c>
-      <c r="R23" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" t="s">
         <v>272</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>273</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24" t="s">
+        <v>273</v>
+      </c>
+      <c r="F24" t="s">
+        <v>350</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
         <v>274</v>
       </c>
-      <c r="D24" t="s">
-        <v>274</v>
-      </c>
-      <c r="E24" t="s">
-        <v>274</v>
-      </c>
-      <c r="F24" t="s">
-        <v>351</v>
-      </c>
-      <c r="G24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>275</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>276</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>277</v>
-      </c>
-      <c r="K24" t="s">
-        <v>278</v>
       </c>
       <c r="L24" t="s">
         <v>22</v>
       </c>
       <c r="M24" t="s">
+        <v>278</v>
+      </c>
+      <c r="N24" t="s">
         <v>279</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
+        <v>273</v>
+      </c>
+      <c r="P24" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>385</v>
+      </c>
+      <c r="R24" t="s">
         <v>280</v>
-      </c>
-      <c r="O24" t="s">
-        <v>274</v>
-      </c>
-      <c r="P24" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>386</v>
-      </c>
-      <c r="R24" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" t="s">
         <v>282</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>283</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" t="s">
+        <v>283</v>
+      </c>
+      <c r="F25" t="s">
+        <v>350</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
         <v>284</v>
       </c>
-      <c r="D25" t="s">
-        <v>284</v>
-      </c>
-      <c r="E25" t="s">
-        <v>284</v>
-      </c>
-      <c r="F25" t="s">
-        <v>351</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>285</v>
       </c>
-      <c r="I25" t="s">
-        <v>286</v>
-      </c>
       <c r="J25" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K25" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L25" t="s">
         <v>22</v>
       </c>
       <c r="M25" t="s">
+        <v>286</v>
+      </c>
+      <c r="N25" t="s">
         <v>287</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
+        <v>283</v>
+      </c>
+      <c r="P25" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>386</v>
+      </c>
+      <c r="R25" t="s">
         <v>288</v>
-      </c>
-      <c r="O25" t="s">
-        <v>284</v>
-      </c>
-      <c r="P25" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>387</v>
-      </c>
-      <c r="R25" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B26" t="s">
         <v>290</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>291</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" t="s">
+        <v>291</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
         <v>292</v>
       </c>
-      <c r="D26" t="s">
-        <v>292</v>
-      </c>
-      <c r="E26" t="s">
-        <v>292</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
         <v>293</v>
       </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>294</v>
       </c>
-      <c r="N26" t="s">
-        <v>295</v>
-      </c>
       <c r="O26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s">
         <v>21</v>
@@ -3031,226 +3031,226 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" t="s">
         <v>296</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>297</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F27" t="s">
+        <v>351</v>
+      </c>
+      <c r="G27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s">
         <v>298</v>
       </c>
-      <c r="D27" t="s">
-        <v>298</v>
-      </c>
-      <c r="E27" t="s">
-        <v>298</v>
-      </c>
-      <c r="F27" t="s">
-        <v>352</v>
-      </c>
-      <c r="G27" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>299</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
+        <v>364</v>
+      </c>
+      <c r="K27" t="s">
         <v>300</v>
-      </c>
-      <c r="J27" t="s">
-        <v>365</v>
-      </c>
-      <c r="K27" t="s">
-        <v>301</v>
       </c>
       <c r="L27" t="s">
         <v>22</v>
       </c>
       <c r="M27" t="s">
+        <v>301</v>
+      </c>
+      <c r="N27" t="s">
         <v>302</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
+        <v>297</v>
+      </c>
+      <c r="P27" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>387</v>
+      </c>
+      <c r="R27" t="s">
         <v>303</v>
-      </c>
-      <c r="O27" t="s">
-        <v>298</v>
-      </c>
-      <c r="P27" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>388</v>
-      </c>
-      <c r="R27" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>304</v>
+      </c>
+      <c r="B28" t="s">
         <v>305</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>306</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>306</v>
+      </c>
+      <c r="E28" t="s">
+        <v>306</v>
+      </c>
+      <c r="F28" t="s">
+        <v>352</v>
+      </c>
+      <c r="G28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s">
         <v>307</v>
       </c>
-      <c r="D28" t="s">
-        <v>307</v>
-      </c>
-      <c r="E28" t="s">
-        <v>307</v>
-      </c>
-      <c r="F28" t="s">
-        <v>353</v>
-      </c>
-      <c r="G28" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>308</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
         <v>309</v>
-      </c>
-      <c r="J28" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" t="s">
-        <v>310</v>
       </c>
       <c r="L28" t="s">
         <v>22</v>
       </c>
       <c r="M28" t="s">
+        <v>310</v>
+      </c>
+      <c r="N28" t="s">
+        <v>391</v>
+      </c>
+      <c r="O28" t="s">
         <v>311</v>
       </c>
-      <c r="N28" t="s">
-        <v>392</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>312</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
+        <v>388</v>
+      </c>
+      <c r="R28" t="s">
         <v>313</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>389</v>
-      </c>
-      <c r="R28" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>314</v>
+      </c>
+      <c r="B29" t="s">
         <v>315</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>316</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>316</v>
+      </c>
+      <c r="E29" t="s">
+        <v>316</v>
+      </c>
+      <c r="F29" t="s">
+        <v>353</v>
+      </c>
+      <c r="G29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" t="s">
         <v>317</v>
       </c>
-      <c r="D29" t="s">
-        <v>317</v>
-      </c>
-      <c r="E29" t="s">
-        <v>317</v>
-      </c>
-      <c r="F29" t="s">
-        <v>354</v>
-      </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>318</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" t="s">
         <v>319</v>
-      </c>
-      <c r="J29" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" t="s">
-        <v>320</v>
       </c>
       <c r="L29" t="s">
         <v>22</v>
       </c>
       <c r="M29" t="s">
+        <v>320</v>
+      </c>
+      <c r="N29" t="s">
+        <v>392</v>
+      </c>
+      <c r="O29" t="s">
         <v>321</v>
       </c>
-      <c r="N29" t="s">
-        <v>393</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>322</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
+        <v>389</v>
+      </c>
+      <c r="R29" t="s">
         <v>323</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>390</v>
-      </c>
-      <c r="R29" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>324</v>
+      </c>
+      <c r="B30" t="s">
         <v>325</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>326</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>326</v>
+      </c>
+      <c r="E30" t="s">
+        <v>326</v>
+      </c>
+      <c r="F30" t="s">
+        <v>354</v>
+      </c>
+      <c r="G30" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" t="s">
         <v>327</v>
       </c>
-      <c r="D30" t="s">
-        <v>327</v>
-      </c>
-      <c r="E30" t="s">
-        <v>327</v>
-      </c>
-      <c r="F30" t="s">
-        <v>355</v>
-      </c>
-      <c r="G30" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>328</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" t="s">
         <v>329</v>
       </c>
-      <c r="J30" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" t="s">
         <v>330</v>
       </c>
-      <c r="L30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
+        <v>393</v>
+      </c>
+      <c r="O30" t="s">
         <v>331</v>
       </c>
-      <c r="N30" t="s">
-        <v>394</v>
-      </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>332</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
         <v>333</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" t="s">
-        <v>334</v>
       </c>
     </row>
   </sheetData>
